--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-12</t>
+          <t>Ventas 2025-09-01 / 2025-09-13</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>66788.17999999999</v>
+        <v>72110.14</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>27601.4</v>
+        <v>29521.33</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>12797.67</v>
+        <v>15263.99</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>38050.02</v>
+        <v>42334.38</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>13412.72</v>
+        <v>15256.19</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>48280.82</v>
+        <v>53299.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>47254.57</v>
+        <v>53116.25</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-13</t>
+          <t>Ventas 2025-09-01 / 2025-09-14</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>72110.14</v>
+        <v>78194.82000000001</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>29521.33</v>
+        <v>32903.87</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15263.99</v>
+        <v>16752.85</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>42334.38</v>
+        <v>45578.81</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>15256.19</v>
+        <v>16659.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>53299.55</v>
+        <v>58022.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>53116.25</v>
+        <v>57836.83</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-14</t>
+          <t>Ventas 2025-09-01 / 2025-09-19</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>78194.82000000001</v>
+        <v>102943.23</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>32903.87</v>
+        <v>43155.65</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>16752.85</v>
+        <v>22129.85</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>45578.81</v>
+        <v>59698.49</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>16659.55</v>
+        <v>20250.69</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>58022.55</v>
+        <v>79204.09</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>57836.83</v>
+        <v>74595.50999999999</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-19</t>
+          <t>Ventas 2025-09-01 / 2025-09-20</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>102943.23</v>
+        <v>111209.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>43155.65</v>
+        <v>46165.25</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>22129.85</v>
+        <v>24289.63</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>59698.49</v>
+        <v>64043.81</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>20250.69</v>
+        <v>21993.29</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>79204.09</v>
+        <v>84086.17999999999</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>74595.50999999999</v>
+        <v>80435.11</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-20</t>
+          <t>Ventas 2025-09-01 / 2025-09-21</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>111209.45</v>
+        <v>115379.14</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>46165.25</v>
+        <v>48364.79</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>24289.63</v>
+        <v>25693.26</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>64043.81</v>
+        <v>67257.72</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>21993.29</v>
+        <v>23235.38</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>84086.17999999999</v>
+        <v>88213.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>80435.11</v>
+        <v>85041.2</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-21</t>
+          <t>Ventas 2025-09-01 / 2025-09-22</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>115379.14</v>
+        <v>120027.09</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>48364.79</v>
+        <v>50590.48</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>25693.26</v>
+        <v>26316.54</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>67257.72</v>
+        <v>69841.72</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>23235.38</v>
+        <v>24032.39</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>88213.55</v>
+        <v>91290.82000000001</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>85041.2</v>
+        <v>88047.95</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-22</t>
+          <t>Ventas 2025-09-01 / 2025-09-23</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>120027.09</v>
+        <v>124770.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>50590.48</v>
+        <v>52592.03</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>26316.54</v>
+        <v>27291.22</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>69841.72</v>
+        <v>72407.99000000001</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>24032.39</v>
+        <v>24608.49</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>91290.82000000001</v>
+        <v>94939.09</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>88047.95</v>
+        <v>90912.89999999999</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-23</t>
+          <t>Ventas 2025-09-01 / 2025-09-24</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>124770.45</v>
+        <v>131150.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>52592.03</v>
+        <v>56088.94</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>27291.22</v>
+        <v>28029.81</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>72407.99000000001</v>
+        <v>75184.81</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>24608.49</v>
+        <v>25183</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>94939.09</v>
+        <v>98817.36</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>90912.89999999999</v>
+        <v>93791.17</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-24</t>
+          <t>Ventas 2025-09-01 / 2025-09-25</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>131150.95</v>
+        <v>134992.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>56088.94</v>
+        <v>57861.89</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>28029.81</v>
+        <v>28779.23</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>75184.81</v>
+        <v>78080.03999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>25183</v>
+        <v>25986.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>98817.36</v>
+        <v>103117.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>93791.17</v>
+        <v>96911.62</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-25</t>
+          <t>Ventas 2025-09-01 / 2025-09-26</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>134992.55</v>
+        <v>140272.41</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>57861.89</v>
+        <v>59988.06</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>28779.23</v>
+        <v>30308.73</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>78080.03999999999</v>
+        <v>81384.22</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>25986.45</v>
+        <v>26848.6</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>103117.82</v>
+        <v>108041.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>96911.62</v>
+        <v>101284.32</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-26</t>
+          <t>Ventas 2025-09-01 / 2025-09-27</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>140272.41</v>
+        <v>147898.64</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>59988.06</v>
+        <v>62769.87</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>30308.73</v>
+        <v>32624.23</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>81384.22</v>
+        <v>85054.99000000001</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>26848.6</v>
+        <v>28210.25</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>108041.64</v>
+        <v>113258.18</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>101284.32</v>
+        <v>107350.74</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-27</t>
+          <t>Ventas 2025-09-01 / 2025-09-28</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>147898.64</v>
+        <v>154554.86</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>62769.87</v>
+        <v>65581.83</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>32624.23</v>
+        <v>33972.23</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>85054.99000000001</v>
+        <v>88205.49000000001</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>28210.25</v>
+        <v>29390.65</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>113258.18</v>
+        <v>117693</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>107350.74</v>
+        <v>111405.51</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-28</t>
+          <t>Ventas 2025-09-01 / 2025-09-29</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>154554.86</v>
+        <v>159107.91</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>65581.83</v>
+        <v>67564.64999999999</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>33972.23</v>
+        <v>34901.91</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>88205.49000000001</v>
+        <v>90891.22</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>29390.65</v>
+        <v>30133.47</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>117693</v>
+        <v>121692.73</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>111405.51</v>
+        <v>112257.89</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-29</t>
+          <t>Ventas 2025-09-01 / 2025-09-30</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>159107.91</v>
+        <v>164023.79</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>67564.64999999999</v>
+        <v>69487.96000000001</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>34901.91</v>
+        <v>35778.95</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>90891.22</v>
+        <v>93232.17</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>30133.47</v>
+        <v>30708.66</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>121692.73</v>
+        <v>125883.91</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>112257.89</v>
+        <v>114595.81</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-30</t>
+          <t>Ventas 2025-10-01 / 2025-10-01</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>164023.79</v>
+        <v>4695.91</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>69487.96000000001</v>
+        <v>1853.95</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>35778.95</v>
+        <v>613.1799999999999</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>93232.17</v>
+        <v>2231.23</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>30708.66</v>
+        <v>616.6900000000001</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>125883.91</v>
+        <v>3869.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>114595.81</v>
+        <v>3367.05</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-01</t>
+          <t>Ventas 2025-10-01 / 2025-10-02</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4695.91</v>
+        <v>9433.77</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1853.95</v>
+        <v>4103.55</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>613.1799999999999</v>
+        <v>1449.6</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>2231.23</v>
+        <v>4497.68</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>616.6900000000001</v>
+        <v>1224.7</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3869.64</v>
+        <v>7837.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>3367.05</v>
+        <v>6513.81</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-02</t>
+          <t>Ventas 2025-10-01 / 2025-10-03</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>9433.77</v>
+        <v>15451.64</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4103.55</v>
+        <v>6267.05</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1449.6</v>
+        <v>2485.46</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>4497.68</v>
+        <v>7451.73</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1224.7</v>
+        <v>2030.95</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>7837.64</v>
+        <v>12233.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>6513.81</v>
+        <v>10477.52</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-03</t>
+          <t>Ventas 2025-10-01 / 2025-10-04</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>15451.64</v>
+        <v>23426.5</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6267.05</v>
+        <v>9009.27</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2485.46</v>
+        <v>4338.78</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>7451.73</v>
+        <v>11226.41</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2030.95</v>
+        <v>3721.05</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>12233.55</v>
+        <v>17353.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>10477.52</v>
+        <v>16883.55</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-04</t>
+          <t>Ventas 2025-10-01 / 2025-10-05</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>23426.5</v>
+        <v>29695.68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>9009.27</v>
+        <v>11729.32</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>4338.78</v>
+        <v>5860.19</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>11226.41</v>
+        <v>13999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3721.05</v>
+        <v>4639.01</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>17353.82</v>
+        <v>21795.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>16883.55</v>
+        <v>21291.17</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-05</t>
+          <t>Ventas 2025-10-01 / 2025-10-06</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>29695.68</v>
+        <v>34100.05</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>11729.32</v>
+        <v>13760.35</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>5860.19</v>
+        <v>6553.65</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>13999</v>
+        <v>16473.73</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4639.01</v>
+        <v>5301.1</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>21795.55</v>
+        <v>25981.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>21291.17</v>
+        <v>24198.52</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-06</t>
+          <t>Ventas 2025-10-01 / 2025-10-07</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>34100.05</v>
+        <v>38472.68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>13760.35</v>
+        <v>15547.63</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>6553.65</v>
+        <v>7434.55</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>16473.73</v>
+        <v>18804.95</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>5301.1</v>
+        <v>5951.84</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>25981.82</v>
+        <v>30087.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>24198.52</v>
+        <v>27047.93</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-07</t>
+          <t>Ventas 2025-10-01 / 2025-10-08</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>38472.68</v>
+        <v>42970.59</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>15547.63</v>
+        <v>17222.67</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>7434.55</v>
+        <v>8151.05</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>18804.95</v>
+        <v>20998.23</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>5951.84</v>
+        <v>6414.88</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>30087.64</v>
+        <v>34370.91</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>27047.93</v>
+        <v>30752.45</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-08</t>
+          <t>Ventas 2025-10-01 / 2025-10-09</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>42970.59</v>
+        <v>46081.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>17222.67</v>
+        <v>18940.45</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>8151.05</v>
+        <v>8576.65</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>20998.23</v>
+        <v>23239.41</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>6414.88</v>
+        <v>6983.57</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>34370.91</v>
+        <v>39366.18</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>30752.45</v>
+        <v>34446.34</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-09</t>
+          <t>Ventas 2025-10-01 / 2025-10-10</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>46081.55</v>
+        <v>51569.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>18940.45</v>
+        <v>21404.35</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>8576.65</v>
+        <v>9332.83</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>23239.41</v>
+        <v>26246.14</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>6983.57</v>
+        <v>7937.21</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>39366.18</v>
+        <v>44408.09</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>34446.34</v>
+        <v>37393.44</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-10</t>
+          <t>Ventas 2025-10-01 / 2025-10-11</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>51569.45</v>
+        <v>58789.05</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>21404.35</v>
+        <v>24038.06</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9332.83</v>
+        <v>11034.96</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>26246.14</v>
+        <v>29740.59</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>7937.21</v>
+        <v>9315.98</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>44408.09</v>
+        <v>50234.18</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>37393.44</v>
+        <v>40086.47</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-11</t>
+          <t>Ventas 2025-10-01 / 2025-10-12</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>58789.05</v>
+        <v>64927.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>24038.06</v>
+        <v>26866.2</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>11034.96</v>
+        <v>13157.01</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>29740.59</v>
+        <v>33302.14</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>9315.98</v>
+        <v>10429.3</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>50234.18</v>
+        <v>54773.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>40086.47</v>
+        <v>44454.6</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-12</t>
+          <t>Ventas 2025-10-01 / 2025-10-13</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>64927.55</v>
+        <v>69178.91</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>26866.2</v>
+        <v>28628.65</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>13157.01</v>
+        <v>14274.1</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>33302.14</v>
+        <v>36026.91</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>10429.3</v>
+        <v>11761.85</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>54773.82</v>
+        <v>59166.09</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>44454.6</v>
+        <v>45986.27</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-13</t>
+          <t>Ventas 2025-10-01 / 2025-10-14</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>69178.91</v>
+        <v>72756.23</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>28628.65</v>
+        <v>30346.29</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>14274.1</v>
+        <v>15136.74</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>36026.91</v>
+        <v>38109.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>11761.85</v>
+        <v>12318.57</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>59166.09</v>
+        <v>63020.36</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>45986.27</v>
+        <v>48474.22</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-14</t>
+          <t>Ventas 2025-10-01 / 2025-10-15</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>72756.23</v>
+        <v>77021.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>30346.29</v>
+        <v>31978.45</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15136.74</v>
+        <v>15865.1</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>38109.09</v>
+        <v>40479.45</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>12318.57</v>
+        <v>13053.99</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>63020.36</v>
+        <v>66934.91</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>48474.22</v>
+        <v>51504.05</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-15</t>
+          <t>Ventas 2025-10-01 / 2025-10-16</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>77021.27</v>
+        <v>80947.09</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>31978.45</v>
+        <v>33574.36</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15865.1</v>
+        <v>16565.42</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>40479.45</v>
+        <v>42654.73</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>13053.99</v>
+        <v>13703.69</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>66934.91</v>
+        <v>71254</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>51504.05</v>
+        <v>54225.71</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-16</t>
+          <t>Ventas 2025-10-01 / 2025-10-19</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>80947.09</v>
+        <v>98026.94</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>33574.36</v>
+        <v>41860.38</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>16565.42</v>
+        <v>20427.92</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>42654.73</v>
+        <v>51796.91</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>13703.69</v>
+        <v>16530.82</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>71254</v>
+        <v>85932.45</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>54225.71</v>
+        <v>70074.10000000001</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-19</t>
+          <t>Ventas 2025-10-01 / 2025-10-20</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>98026.94</v>
+        <v>102529.12</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>41860.38</v>
+        <v>44127.24</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>20427.92</v>
+        <v>21035.87</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>51796.91</v>
+        <v>54188.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>16530.82</v>
+        <v>17396.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>85932.45</v>
+        <v>90036.45</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>70074.10000000001</v>
+        <v>73390.69</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-20</t>
+          <t>Ventas 2025-10-01 / 2025-10-21</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>102529.12</v>
+        <v>107430.75</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>44127.24</v>
+        <v>46467.23</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>21035.87</v>
+        <v>21780.65</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>54188.64</v>
+        <v>56832.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>17396.73</v>
+        <v>18179.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>90036.45</v>
+        <v>94001</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>73390.69</v>
+        <v>76554.59</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-21</t>
+          <t>Ventas 2025-10-01 / 2025-10-22</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>107430.75</v>
+        <v>112573.8</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>46467.23</v>
+        <v>48780.32</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>21780.65</v>
+        <v>22437.96</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>56832.64</v>
+        <v>59301</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>18179.73</v>
+        <v>18868.33</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>94001</v>
+        <v>98186.91</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>76554.59</v>
+        <v>79380.39999999999</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-22</t>
+          <t>Ventas 2025-10-01 / 2025-10-23</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>112573.8</v>
+        <v>116940.07</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>48780.32</v>
+        <v>51272.05</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>22437.96</v>
+        <v>23235.69</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>59301</v>
+        <v>62128.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>18868.33</v>
+        <v>19578.56</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>98186.91</v>
+        <v>102760.09</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>79380.39999999999</v>
+        <v>82428.67</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-23</t>
+          <t>Ventas 2025-10-01 / 2025-10-24</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>116940.07</v>
+        <v>122545.57</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>51272.05</v>
+        <v>53218.91</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>23235.69</v>
+        <v>24541.33</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>62128.36</v>
+        <v>65296.27</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>19578.56</v>
+        <v>20348.79</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>102760.09</v>
+        <v>107403</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>82428.67</v>
+        <v>86450.03</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-24</t>
+          <t>Ventas 2025-10-01 / 2025-10-25</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>122545.57</v>
+        <v>128924.71</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>53218.91</v>
+        <v>55813.53</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>24541.33</v>
+        <v>26714.42</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>65296.27</v>
+        <v>69043.17999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>20348.79</v>
+        <v>21668.34</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>107403</v>
+        <v>111873.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>86450.03</v>
+        <v>92215.28</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-25</t>
+          <t>Ventas 2025-10-01 / 2025-10-26</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>128924.71</v>
+        <v>134160.68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>55813.53</v>
+        <v>58455.62</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>26714.42</v>
+        <v>27575.15</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>69043.17999999999</v>
+        <v>72167.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>21668.34</v>
+        <v>22716.84</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>111873.82</v>
+        <v>116309.73</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>92215.28</v>
+        <v>95744.71000000001</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-26</t>
+          <t>Ventas 2025-10-01 / 2025-10-27</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>134160.68</v>
+        <v>138151.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>58455.62</v>
+        <v>60707.28</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>27575.15</v>
+        <v>28308.92</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>72167.36</v>
+        <v>74388.17999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>22716.84</v>
+        <v>23375.2</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>116309.73</v>
+        <v>121093.91</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>95744.71000000001</v>
+        <v>98807.69</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-27</t>
+          <t>Ventas 2025-10-01 / 2025-10-28</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>138151.45</v>
+        <v>142479.21</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>60707.28</v>
+        <v>62564.64</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>28308.92</v>
+        <v>28780.69</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>74388.17999999999</v>
+        <v>75983.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>23375.2</v>
+        <v>23848.2</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>121093.91</v>
+        <v>124945.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>98807.69</v>
+        <v>101845.4</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-28</t>
+          <t>Ventas 2025-10-01 / 2025-10-29</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>142479.21</v>
+        <v>146415.12</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>62564.64</v>
+        <v>64353.86</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>28780.69</v>
+        <v>29154.51</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>75983.64</v>
+        <v>77138.91</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>23848.2</v>
+        <v>24091.75</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>124945.64</v>
+        <v>128490.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>101845.4</v>
+        <v>104538.19</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-29</t>
+          <t>Ventas 2025-10-01 / 2025-10-30</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>146415.12</v>
+        <v>150816.62</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>64353.86</v>
+        <v>66172.5</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>29154.51</v>
+        <v>29822.87</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>77138.91</v>
+        <v>79143.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>24091.75</v>
+        <v>24829.84</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>128490.64</v>
+        <v>131934.27</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>104538.19</v>
+        <v>107237.9</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
